--- a/PraticaW1D1_GGabriele.xlsx
+++ b/PraticaW1D1_GGabriele.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gabri\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gabri\Desktop\Epicode-Dapt0326\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADE341E7-B151-4AAD-8BA3-B8C0DD7B5124}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDB26A2E-1B79-4333-B748-F85BFE7B18D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CC2D0ADA-4E80-42B2-8D69-B90DD28C34B4}"/>
+    <workbookView xWindow="-24120" yWindow="1725" windowWidth="24240" windowHeight="13020" xr2:uid="{CC2D0ADA-4E80-42B2-8D69-B90DD28C34B4}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -343,10 +343,10 @@
   <tableColumns count="4">
     <tableColumn id="2" xr3:uid="{D8FBA505-ABCD-4EF1-9C07-B9566589C1A1}" name="Posizione valore"/>
     <tableColumn id="1" xr3:uid="{D53B25E8-0B5D-4CD8-82BB-CF304CC646E5}" name="Voti studenti"/>
-    <tableColumn id="3" xr3:uid="{2A3B9973-BBEB-47B8-AB25-C6FD766AE176}" name="Scarti media" dataDxfId="0">
+    <tableColumn id="3" xr3:uid="{2A3B9973-BBEB-47B8-AB25-C6FD766AE176}" name="Scarti media" dataDxfId="1">
       <calculatedColumnFormula>Tabella1[[#This Row],[Voti studenti]]-$J$6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{4D0DDA63-C00C-466F-BE21-BF71134AA5FA}" name="Quadrati degli scarti" dataDxfId="1">
+    <tableColumn id="4" xr3:uid="{4D0DDA63-C00C-466F-BE21-BF71134AA5FA}" name="Quadrati degli scarti" dataDxfId="0">
       <calculatedColumnFormula>POWER(Tabella1[[#This Row],[Scarti media]],2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1047,6 +1047,11 @@
         <v>21</v>
       </c>
       <c r="D24">
+        <f>COUNTIFS(Tabella1[Voti studenti],"&gt;="&amp;B24,Tabella1[Voti studenti],"&lt;="&amp;C24)</f>
+        <v>1</v>
+      </c>
+      <c r="E24" cm="1">
+        <f t="array" ref="E24:E27">FREQUENCY(Tabella1[Voti studenti],C24:C26)</f>
         <v>1</v>
       </c>
       <c r="J24">
@@ -1062,6 +1067,10 @@
         <v>25</v>
       </c>
       <c r="D25">
+        <f>COUNTIFS(Tabella1[Voti studenti],"&gt;="&amp;B25,Tabella1[Voti studenti],"&lt;="&amp;C25)</f>
+        <v>3</v>
+      </c>
+      <c r="E25">
         <v>3</v>
       </c>
     </row>
@@ -1073,10 +1082,17 @@
         <v>30</v>
       </c>
       <c r="D26">
+        <f>COUNTIFS(Tabella1[Voti studenti],"&gt;="&amp;B26,Tabella1[Voti studenti],"&lt;="&amp;C26)</f>
         <v>8</v>
       </c>
+      <c r="E26">
+        <v>8</v>
+      </c>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="E27">
+        <v>0</v>
+      </c>
       <c r="I27" t="s">
         <v>23</v>
       </c>
